--- a/artfynd/A 38440-2021 artfynd.xlsx
+++ b/artfynd/A 38440-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38440-2021 artfynd.xlsx
+++ b/artfynd/A 38440-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>114378619</v>
       </c>
       <c r="B3" t="n">
-        <v>56249</v>
+        <v>56252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>114620257</v>
       </c>
       <c r="B5" t="n">
-        <v>56249</v>
+        <v>56252</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 38440-2021 artfynd.xlsx
+++ b/artfynd/A 38440-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>114378619</v>
       </c>
       <c r="B3" t="n">
-        <v>56252</v>
+        <v>56255</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>114620257</v>
       </c>
       <c r="B5" t="n">
-        <v>56252</v>
+        <v>56255</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
